--- a/artfynd/A 7751-2024 artfynd.xlsx
+++ b/artfynd/A 7751-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105537809</v>
+        <v>105537835</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -715,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489951.416833816</v>
+        <v>489951</v>
       </c>
       <c r="R2" t="n">
-        <v>6531409.185710161</v>
+        <v>6531409</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +747,9 @@
           <t>2009-07-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2009-07-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -796,12 +785,7 @@
         <v>105537861</v>
       </c>
       <c r="B3" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -837,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489951.416833816</v>
+        <v>489951</v>
       </c>
       <c r="R3" t="n">
-        <v>6531409.185710161</v>
+        <v>6531409</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -870,19 +854,9 @@
           <t>2009-07-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2009-07-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -915,37 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105537835</v>
+        <v>105537915</v>
       </c>
       <c r="B4" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489951.416833816</v>
+        <v>489951</v>
       </c>
       <c r="R4" t="n">
-        <v>6531409.185710161</v>
+        <v>6531409</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -992,19 +961,9 @@
           <t>2009-07-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2009-07-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1037,39 +996,30 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105537915</v>
+        <v>105537809</v>
       </c>
       <c r="B5" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>223597</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -1081,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489951.416833816</v>
+        <v>489951</v>
       </c>
       <c r="R5" t="n">
-        <v>6531409.185710161</v>
+        <v>6531409</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1114,19 +1064,9 @@
           <t>2009-07-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2009-07-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 7751-2024 artfynd.xlsx
+++ b/artfynd/A 7751-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105537835</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105537861</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105537915</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,8 +1116,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105537809</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>